--- a/e2e-screenshots/quarter-simulation/downloaded-inventory-report.xlsx
+++ b/e2e-screenshots/quarter-simulation/downloaded-inventory-report.xlsx
@@ -51,7 +51,7 @@
     <t>Age (days)</t>
   </si>
   <si>
-    <t>2026-08-03</t>
+    <t>2026-08-07</t>
   </si>
   <si>
     <t>iPhone 14 Pro</t>
@@ -1372,7 +1372,7 @@
         <v>17</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -1410,7 +1410,7 @@
         <v>17</v>
       </c>
       <c r="L4">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -1448,7 +1448,7 @@
         <v>17</v>
       </c>
       <c r="L5">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -1486,7 +1486,7 @@
         <v>17</v>
       </c>
       <c r="L6">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -1524,7 +1524,7 @@
         <v>17</v>
       </c>
       <c r="L7">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -1562,7 +1562,7 @@
         <v>17</v>
       </c>
       <c r="L8">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -1600,7 +1600,7 @@
         <v>17</v>
       </c>
       <c r="L9">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -1638,7 +1638,7 @@
         <v>17</v>
       </c>
       <c r="L10">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -1676,7 +1676,7 @@
         <v>17</v>
       </c>
       <c r="L11">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -1714,7 +1714,7 @@
         <v>17</v>
       </c>
       <c r="L12">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -1752,7 +1752,7 @@
         <v>17</v>
       </c>
       <c r="L13">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -1790,7 +1790,7 @@
         <v>17</v>
       </c>
       <c r="L14">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -1828,7 +1828,7 @@
         <v>17</v>
       </c>
       <c r="L15">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -1866,7 +1866,7 @@
         <v>17</v>
       </c>
       <c r="L16">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
@@ -1904,7 +1904,7 @@
         <v>17</v>
       </c>
       <c r="L17">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
@@ -1942,7 +1942,7 @@
         <v>17</v>
       </c>
       <c r="L18">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
@@ -1980,7 +1980,7 @@
         <v>17</v>
       </c>
       <c r="L19">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
@@ -2018,7 +2018,7 @@
         <v>17</v>
       </c>
       <c r="L20">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
@@ -2056,7 +2056,7 @@
         <v>17</v>
       </c>
       <c r="L21">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
@@ -2094,7 +2094,7 @@
         <v>17</v>
       </c>
       <c r="L22">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
@@ -2132,7 +2132,7 @@
         <v>17</v>
       </c>
       <c r="L23">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
@@ -2170,7 +2170,7 @@
         <v>17</v>
       </c>
       <c r="L24">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
@@ -2208,7 +2208,7 @@
         <v>17</v>
       </c>
       <c r="L25">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
@@ -2246,7 +2246,7 @@
         <v>17</v>
       </c>
       <c r="L26">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
@@ -2284,7 +2284,7 @@
         <v>17</v>
       </c>
       <c r="L27">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
@@ -2322,7 +2322,7 @@
         <v>17</v>
       </c>
       <c r="L28">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
@@ -2360,7 +2360,7 @@
         <v>17</v>
       </c>
       <c r="L29">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
@@ -2398,7 +2398,7 @@
         <v>17</v>
       </c>
       <c r="L30">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
@@ -2436,7 +2436,7 @@
         <v>17</v>
       </c>
       <c r="L31">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
@@ -2474,7 +2474,7 @@
         <v>17</v>
       </c>
       <c r="L32">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
@@ -2512,7 +2512,7 @@
         <v>17</v>
       </c>
       <c r="L33">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
@@ -2550,7 +2550,7 @@
         <v>17</v>
       </c>
       <c r="L34">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
@@ -2588,7 +2588,7 @@
         <v>17</v>
       </c>
       <c r="L35">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
@@ -2626,7 +2626,7 @@
         <v>17</v>
       </c>
       <c r="L36">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
@@ -2664,7 +2664,7 @@
         <v>17</v>
       </c>
       <c r="L37">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
@@ -2702,7 +2702,7 @@
         <v>17</v>
       </c>
       <c r="L38">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
@@ -2740,7 +2740,7 @@
         <v>17</v>
       </c>
       <c r="L39">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
@@ -2778,7 +2778,7 @@
         <v>17</v>
       </c>
       <c r="L40">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
@@ -2816,7 +2816,7 @@
         <v>17</v>
       </c>
       <c r="L41">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
@@ -2854,7 +2854,7 @@
         <v>17</v>
       </c>
       <c r="L42">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
@@ -2892,7 +2892,7 @@
         <v>17</v>
       </c>
       <c r="L43">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
@@ -2930,7 +2930,7 @@
         <v>17</v>
       </c>
       <c r="L44">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
@@ -2968,7 +2968,7 @@
         <v>17</v>
       </c>
       <c r="L45">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
@@ -3006,7 +3006,7 @@
         <v>17</v>
       </c>
       <c r="L46">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
@@ -3044,7 +3044,7 @@
         <v>17</v>
       </c>
       <c r="L47">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
@@ -3082,7 +3082,7 @@
         <v>17</v>
       </c>
       <c r="L48">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
@@ -3120,7 +3120,7 @@
         <v>17</v>
       </c>
       <c r="L49">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
@@ -3158,7 +3158,7 @@
         <v>17</v>
       </c>
       <c r="L50">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
@@ -3196,7 +3196,7 @@
         <v>17</v>
       </c>
       <c r="L51">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
@@ -3234,7 +3234,7 @@
         <v>17</v>
       </c>
       <c r="L52">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
@@ -3272,7 +3272,7 @@
         <v>17</v>
       </c>
       <c r="L53">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
@@ -3310,7 +3310,7 @@
         <v>17</v>
       </c>
       <c r="L54">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
@@ -3348,7 +3348,7 @@
         <v>17</v>
       </c>
       <c r="L55">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
@@ -3386,7 +3386,7 @@
         <v>17</v>
       </c>
       <c r="L56">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
@@ -3424,7 +3424,7 @@
         <v>17</v>
       </c>
       <c r="L57">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
@@ -3462,7 +3462,7 @@
         <v>17</v>
       </c>
       <c r="L58">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
@@ -3500,7 +3500,7 @@
         <v>17</v>
       </c>
       <c r="L59">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
@@ -3538,7 +3538,7 @@
         <v>17</v>
       </c>
       <c r="L60">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
@@ -3576,7 +3576,7 @@
         <v>17</v>
       </c>
       <c r="L61">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
@@ -3614,7 +3614,7 @@
         <v>17</v>
       </c>
       <c r="L62">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
@@ -3652,7 +3652,7 @@
         <v>17</v>
       </c>
       <c r="L63">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
@@ -3690,7 +3690,7 @@
         <v>17</v>
       </c>
       <c r="L64">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
@@ -3728,7 +3728,7 @@
         <v>17</v>
       </c>
       <c r="L65">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
@@ -3766,7 +3766,7 @@
         <v>17</v>
       </c>
       <c r="L66">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
@@ -3804,7 +3804,7 @@
         <v>17</v>
       </c>
       <c r="L67">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
@@ -3842,7 +3842,7 @@
         <v>17</v>
       </c>
       <c r="L68">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
@@ -3880,7 +3880,7 @@
         <v>17</v>
       </c>
       <c r="L69">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
@@ -3918,7 +3918,7 @@
         <v>17</v>
       </c>
       <c r="L70">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
@@ -3956,7 +3956,7 @@
         <v>17</v>
       </c>
       <c r="L71">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
@@ -3994,7 +3994,7 @@
         <v>17</v>
       </c>
       <c r="L72">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
@@ -4032,7 +4032,7 @@
         <v>17</v>
       </c>
       <c r="L73">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
@@ -4070,7 +4070,7 @@
         <v>17</v>
       </c>
       <c r="L74">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
@@ -4108,7 +4108,7 @@
         <v>17</v>
       </c>
       <c r="L75">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
@@ -4146,7 +4146,7 @@
         <v>17</v>
       </c>
       <c r="L76">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
@@ -4184,7 +4184,7 @@
         <v>17</v>
       </c>
       <c r="L77">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
@@ -4222,7 +4222,7 @@
         <v>17</v>
       </c>
       <c r="L78">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
@@ -4260,7 +4260,7 @@
         <v>17</v>
       </c>
       <c r="L79">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
@@ -4298,7 +4298,7 @@
         <v>17</v>
       </c>
       <c r="L80">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
@@ -4336,7 +4336,7 @@
         <v>17</v>
       </c>
       <c r="L81">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
@@ -4374,7 +4374,7 @@
         <v>17</v>
       </c>
       <c r="L82">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
@@ -4412,7 +4412,7 @@
         <v>17</v>
       </c>
       <c r="L83">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
@@ -4450,7 +4450,7 @@
         <v>17</v>
       </c>
       <c r="L84">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
@@ -4488,7 +4488,7 @@
         <v>17</v>
       </c>
       <c r="L85">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
@@ -4526,7 +4526,7 @@
         <v>17</v>
       </c>
       <c r="L86">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
@@ -4564,7 +4564,7 @@
         <v>17</v>
       </c>
       <c r="L87">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
@@ -4602,7 +4602,7 @@
         <v>17</v>
       </c>
       <c r="L88">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
@@ -4640,7 +4640,7 @@
         <v>17</v>
       </c>
       <c r="L89">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
@@ -4678,7 +4678,7 @@
         <v>17</v>
       </c>
       <c r="L90">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
@@ -4716,7 +4716,7 @@
         <v>17</v>
       </c>
       <c r="L91">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
@@ -4754,7 +4754,7 @@
         <v>17</v>
       </c>
       <c r="L92">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
@@ -4792,7 +4792,7 @@
         <v>17</v>
       </c>
       <c r="L93">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
@@ -4830,7 +4830,7 @@
         <v>17</v>
       </c>
       <c r="L94">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
@@ -4868,7 +4868,7 @@
         <v>17</v>
       </c>
       <c r="L95">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
@@ -4906,7 +4906,7 @@
         <v>17</v>
       </c>
       <c r="L96">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
@@ -4944,7 +4944,7 @@
         <v>17</v>
       </c>
       <c r="L97">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
@@ -4982,7 +4982,7 @@
         <v>17</v>
       </c>
       <c r="L98">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
@@ -5020,7 +5020,7 @@
         <v>17</v>
       </c>
       <c r="L99">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
@@ -5058,7 +5058,7 @@
         <v>17</v>
       </c>
       <c r="L100">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
@@ -5096,7 +5096,7 @@
         <v>17</v>
       </c>
       <c r="L101">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
@@ -5134,7 +5134,7 @@
         <v>17</v>
       </c>
       <c r="L102">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
@@ -5172,7 +5172,7 @@
         <v>17</v>
       </c>
       <c r="L103">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
@@ -5210,7 +5210,7 @@
         <v>17</v>
       </c>
       <c r="L104">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
@@ -5248,7 +5248,7 @@
         <v>17</v>
       </c>
       <c r="L105">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
@@ -5286,7 +5286,7 @@
         <v>17</v>
       </c>
       <c r="L106">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
@@ -5324,7 +5324,7 @@
         <v>17</v>
       </c>
       <c r="L107">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
@@ -5362,7 +5362,7 @@
         <v>17</v>
       </c>
       <c r="L108">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
@@ -5400,7 +5400,7 @@
         <v>17</v>
       </c>
       <c r="L109">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
@@ -5438,7 +5438,7 @@
         <v>17</v>
       </c>
       <c r="L110">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
@@ -5476,7 +5476,7 @@
         <v>17</v>
       </c>
       <c r="L111">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
@@ -5514,7 +5514,7 @@
         <v>17</v>
       </c>
       <c r="L112">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
@@ -5552,7 +5552,7 @@
         <v>17</v>
       </c>
       <c r="L113">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
@@ -5590,7 +5590,7 @@
         <v>17</v>
       </c>
       <c r="L114">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
@@ -5628,7 +5628,7 @@
         <v>17</v>
       </c>
       <c r="L115">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
@@ -5666,7 +5666,7 @@
         <v>17</v>
       </c>
       <c r="L116">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -5761,7 +5761,7 @@
         <v>17</v>
       </c>
       <c r="L2">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -5799,7 +5799,7 @@
         <v>17</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -5837,7 +5837,7 @@
         <v>17</v>
       </c>
       <c r="L4">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -5875,7 +5875,7 @@
         <v>17</v>
       </c>
       <c r="L5">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -5913,7 +5913,7 @@
         <v>17</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -5951,7 +5951,7 @@
         <v>17</v>
       </c>
       <c r="L7">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -5989,7 +5989,7 @@
         <v>17</v>
       </c>
       <c r="L8">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -6027,7 +6027,7 @@
         <v>17</v>
       </c>
       <c r="L9">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -6065,7 +6065,7 @@
         <v>17</v>
       </c>
       <c r="L10">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -6103,7 +6103,7 @@
         <v>17</v>
       </c>
       <c r="L11">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -6141,7 +6141,7 @@
         <v>17</v>
       </c>
       <c r="L12">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -6179,7 +6179,7 @@
         <v>17</v>
       </c>
       <c r="L13">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -6217,7 +6217,7 @@
         <v>17</v>
       </c>
       <c r="L14">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -6255,7 +6255,7 @@
         <v>17</v>
       </c>
       <c r="L15">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -6293,7 +6293,7 @@
         <v>17</v>
       </c>
       <c r="L16">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
@@ -6331,7 +6331,7 @@
         <v>17</v>
       </c>
       <c r="L17">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
@@ -6369,7 +6369,7 @@
         <v>17</v>
       </c>
       <c r="L18">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
@@ -6407,7 +6407,7 @@
         <v>17</v>
       </c>
       <c r="L19">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
@@ -6445,7 +6445,7 @@
         <v>17</v>
       </c>
       <c r="L20">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
@@ -6483,7 +6483,7 @@
         <v>17</v>
       </c>
       <c r="L21">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
@@ -6521,7 +6521,7 @@
         <v>17</v>
       </c>
       <c r="L22">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
@@ -6559,7 +6559,7 @@
         <v>17</v>
       </c>
       <c r="L23">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
@@ -6597,7 +6597,7 @@
         <v>17</v>
       </c>
       <c r="L24">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
@@ -6635,7 +6635,7 @@
         <v>17</v>
       </c>
       <c r="L25">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
@@ -6673,7 +6673,7 @@
         <v>17</v>
       </c>
       <c r="L26">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
@@ -6711,7 +6711,7 @@
         <v>17</v>
       </c>
       <c r="L27">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
@@ -6749,7 +6749,7 @@
         <v>17</v>
       </c>
       <c r="L28">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
@@ -6787,7 +6787,7 @@
         <v>17</v>
       </c>
       <c r="L29">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
@@ -6825,7 +6825,7 @@
         <v>17</v>
       </c>
       <c r="L30">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
@@ -6863,7 +6863,7 @@
         <v>17</v>
       </c>
       <c r="L31">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
@@ -6901,7 +6901,7 @@
         <v>17</v>
       </c>
       <c r="L32">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
@@ -6939,7 +6939,7 @@
         <v>17</v>
       </c>
       <c r="L33">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
@@ -6977,7 +6977,7 @@
         <v>17</v>
       </c>
       <c r="L34">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
@@ -7015,7 +7015,7 @@
         <v>17</v>
       </c>
       <c r="L35">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
@@ -7053,7 +7053,7 @@
         <v>17</v>
       </c>
       <c r="L36">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
@@ -7091,7 +7091,7 @@
         <v>17</v>
       </c>
       <c r="L37">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
@@ -7129,7 +7129,7 @@
         <v>17</v>
       </c>
       <c r="L38">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
@@ -7167,7 +7167,7 @@
         <v>17</v>
       </c>
       <c r="L39">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
@@ -7205,7 +7205,7 @@
         <v>17</v>
       </c>
       <c r="L40">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
@@ -7243,7 +7243,7 @@
         <v>17</v>
       </c>
       <c r="L41">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
@@ -7281,7 +7281,7 @@
         <v>17</v>
       </c>
       <c r="L42">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
@@ -7319,7 +7319,7 @@
         <v>17</v>
       </c>
       <c r="L43">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
@@ -7357,7 +7357,7 @@
         <v>17</v>
       </c>
       <c r="L44">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
@@ -7395,7 +7395,7 @@
         <v>17</v>
       </c>
       <c r="L45">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
@@ -7433,7 +7433,7 @@
         <v>17</v>
       </c>
       <c r="L46">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
@@ -7471,7 +7471,7 @@
         <v>17</v>
       </c>
       <c r="L47">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
@@ -7509,7 +7509,7 @@
         <v>17</v>
       </c>
       <c r="L48">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
@@ -7547,7 +7547,7 @@
         <v>17</v>
       </c>
       <c r="L49">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
@@ -7585,7 +7585,7 @@
         <v>17</v>
       </c>
       <c r="L50">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
@@ -7623,7 +7623,7 @@
         <v>17</v>
       </c>
       <c r="L51">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
@@ -7661,7 +7661,7 @@
         <v>17</v>
       </c>
       <c r="L52">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
@@ -7699,7 +7699,7 @@
         <v>17</v>
       </c>
       <c r="L53">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
@@ -7737,7 +7737,7 @@
         <v>17</v>
       </c>
       <c r="L54">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
@@ -7775,7 +7775,7 @@
         <v>17</v>
       </c>
       <c r="L55">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
@@ -7813,7 +7813,7 @@
         <v>17</v>
       </c>
       <c r="L56">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
@@ -7851,7 +7851,7 @@
         <v>17</v>
       </c>
       <c r="L57">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
@@ -7889,7 +7889,7 @@
         <v>17</v>
       </c>
       <c r="L58">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
@@ -7927,7 +7927,7 @@
         <v>17</v>
       </c>
       <c r="L59">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
@@ -7965,7 +7965,7 @@
         <v>17</v>
       </c>
       <c r="L60">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
@@ -8003,7 +8003,7 @@
         <v>17</v>
       </c>
       <c r="L61">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
@@ -8041,7 +8041,7 @@
         <v>17</v>
       </c>
       <c r="L62">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
@@ -8079,7 +8079,7 @@
         <v>17</v>
       </c>
       <c r="L63">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
@@ -8117,7 +8117,7 @@
         <v>17</v>
       </c>
       <c r="L64">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
@@ -8155,7 +8155,7 @@
         <v>17</v>
       </c>
       <c r="L65">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
@@ -8193,7 +8193,7 @@
         <v>17</v>
       </c>
       <c r="L66">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
@@ -8231,7 +8231,7 @@
         <v>17</v>
       </c>
       <c r="L67">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
@@ -8269,7 +8269,7 @@
         <v>17</v>
       </c>
       <c r="L68">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
@@ -8307,7 +8307,7 @@
         <v>17</v>
       </c>
       <c r="L69">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
@@ -8345,7 +8345,7 @@
         <v>17</v>
       </c>
       <c r="L70">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
@@ -8383,7 +8383,7 @@
         <v>17</v>
       </c>
       <c r="L71">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
@@ -8421,7 +8421,7 @@
         <v>17</v>
       </c>
       <c r="L72">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
@@ -8459,7 +8459,7 @@
         <v>17</v>
       </c>
       <c r="L73">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
@@ -8497,7 +8497,7 @@
         <v>17</v>
       </c>
       <c r="L74">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
@@ -8535,7 +8535,7 @@
         <v>17</v>
       </c>
       <c r="L75">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
@@ -8573,7 +8573,7 @@
         <v>17</v>
       </c>
       <c r="L76">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
@@ -8611,7 +8611,7 @@
         <v>17</v>
       </c>
       <c r="L77">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
@@ -8649,7 +8649,7 @@
         <v>17</v>
       </c>
       <c r="L78">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
@@ -8687,7 +8687,7 @@
         <v>17</v>
       </c>
       <c r="L79">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
@@ -8725,7 +8725,7 @@
         <v>17</v>
       </c>
       <c r="L80">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
@@ -8763,7 +8763,7 @@
         <v>17</v>
       </c>
       <c r="L81">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
@@ -8801,7 +8801,7 @@
         <v>17</v>
       </c>
       <c r="L82">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
@@ -8839,7 +8839,7 @@
         <v>17</v>
       </c>
       <c r="L83">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
@@ -8877,7 +8877,7 @@
         <v>17</v>
       </c>
       <c r="L84">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
@@ -8915,7 +8915,7 @@
         <v>17</v>
       </c>
       <c r="L85">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
@@ -8953,7 +8953,7 @@
         <v>17</v>
       </c>
       <c r="L86">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
@@ -8991,7 +8991,7 @@
         <v>17</v>
       </c>
       <c r="L87">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
@@ -9029,7 +9029,7 @@
         <v>17</v>
       </c>
       <c r="L88">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
@@ -9067,7 +9067,7 @@
         <v>17</v>
       </c>
       <c r="L89">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
@@ -9105,7 +9105,7 @@
         <v>17</v>
       </c>
       <c r="L90">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
@@ -9143,7 +9143,7 @@
         <v>17</v>
       </c>
       <c r="L91">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
@@ -9181,7 +9181,7 @@
         <v>17</v>
       </c>
       <c r="L92">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
@@ -9219,7 +9219,7 @@
         <v>17</v>
       </c>
       <c r="L93">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
@@ -9257,7 +9257,7 @@
         <v>17</v>
       </c>
       <c r="L94">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
@@ -9295,7 +9295,7 @@
         <v>17</v>
       </c>
       <c r="L95">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
@@ -9333,7 +9333,7 @@
         <v>17</v>
       </c>
       <c r="L96">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
@@ -9371,7 +9371,7 @@
         <v>17</v>
       </c>
       <c r="L97">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
@@ -9409,7 +9409,7 @@
         <v>17</v>
       </c>
       <c r="L98">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
@@ -9447,7 +9447,7 @@
         <v>17</v>
       </c>
       <c r="L99">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
@@ -9485,7 +9485,7 @@
         <v>17</v>
       </c>
       <c r="L100">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
@@ -9523,7 +9523,7 @@
         <v>17</v>
       </c>
       <c r="L101">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
@@ -9561,7 +9561,7 @@
         <v>17</v>
       </c>
       <c r="L102">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
@@ -9599,7 +9599,7 @@
         <v>17</v>
       </c>
       <c r="L103">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
@@ -9637,7 +9637,7 @@
         <v>17</v>
       </c>
       <c r="L104">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
@@ -9675,7 +9675,7 @@
         <v>17</v>
       </c>
       <c r="L105">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
@@ -9713,7 +9713,7 @@
         <v>17</v>
       </c>
       <c r="L106">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
@@ -9751,7 +9751,7 @@
         <v>17</v>
       </c>
       <c r="L107">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
@@ -9789,7 +9789,7 @@
         <v>17</v>
       </c>
       <c r="L108">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
@@ -9827,7 +9827,7 @@
         <v>17</v>
       </c>
       <c r="L109">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
@@ -9865,7 +9865,7 @@
         <v>17</v>
       </c>
       <c r="L110">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
@@ -9903,7 +9903,7 @@
         <v>17</v>
       </c>
       <c r="L111">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
@@ -9941,7 +9941,7 @@
         <v>17</v>
       </c>
       <c r="L112">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
@@ -9979,7 +9979,7 @@
         <v>17</v>
       </c>
       <c r="L113">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
@@ -10017,7 +10017,7 @@
         <v>17</v>
       </c>
       <c r="L114">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
@@ -10055,7 +10055,7 @@
         <v>17</v>
       </c>
       <c r="L115">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
@@ -10093,7 +10093,7 @@
         <v>17</v>
       </c>
       <c r="L116">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
@@ -10131,7 +10131,7 @@
         <v>17</v>
       </c>
       <c r="L117">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
@@ -10169,7 +10169,7 @@
         <v>17</v>
       </c>
       <c r="L118">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
@@ -10207,7 +10207,7 @@
         <v>17</v>
       </c>
       <c r="L119">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
@@ -10245,7 +10245,7 @@
         <v>17</v>
       </c>
       <c r="L120">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
@@ -10283,7 +10283,7 @@
         <v>17</v>
       </c>
       <c r="L121">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
@@ -10321,7 +10321,7 @@
         <v>17</v>
       </c>
       <c r="L122">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
@@ -10359,7 +10359,7 @@
         <v>17</v>
       </c>
       <c r="L123">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
@@ -10397,7 +10397,7 @@
         <v>17</v>
       </c>
       <c r="L124">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
@@ -10435,7 +10435,7 @@
         <v>17</v>
       </c>
       <c r="L125">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
@@ -10473,7 +10473,7 @@
         <v>17</v>
       </c>
       <c r="L126">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
@@ -10511,7 +10511,7 @@
         <v>17</v>
       </c>
       <c r="L127">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
@@ -10549,7 +10549,7 @@
         <v>17</v>
       </c>
       <c r="L128">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
@@ -10587,7 +10587,7 @@
         <v>17</v>
       </c>
       <c r="L129">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
@@ -10625,7 +10625,7 @@
         <v>17</v>
       </c>
       <c r="L130">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
@@ -10663,7 +10663,7 @@
         <v>17</v>
       </c>
       <c r="L131">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
@@ -10701,7 +10701,7 @@
         <v>17</v>
       </c>
       <c r="L132">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
@@ -10739,7 +10739,7 @@
         <v>17</v>
       </c>
       <c r="L133">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
@@ -10777,7 +10777,7 @@
         <v>17</v>
       </c>
       <c r="L134">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
@@ -10815,7 +10815,7 @@
         <v>17</v>
       </c>
       <c r="L135">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
@@ -10853,7 +10853,7 @@
         <v>17</v>
       </c>
       <c r="L136">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
@@ -10891,7 +10891,7 @@
         <v>17</v>
       </c>
       <c r="L137">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
@@ -10929,7 +10929,7 @@
         <v>17</v>
       </c>
       <c r="L138">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
@@ -10967,7 +10967,7 @@
         <v>17</v>
       </c>
       <c r="L139">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
@@ -11005,7 +11005,7 @@
         <v>17</v>
       </c>
       <c r="L140">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
@@ -11043,7 +11043,7 @@
         <v>17</v>
       </c>
       <c r="L141">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
@@ -11081,7 +11081,7 @@
         <v>17</v>
       </c>
       <c r="L142">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
@@ -11119,7 +11119,7 @@
         <v>17</v>
       </c>
       <c r="L143">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
@@ -11157,7 +11157,7 @@
         <v>17</v>
       </c>
       <c r="L144">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
@@ -11195,7 +11195,7 @@
         <v>17</v>
       </c>
       <c r="L145">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
@@ -11233,7 +11233,7 @@
         <v>17</v>
       </c>
       <c r="L146">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
@@ -11271,7 +11271,7 @@
         <v>17</v>
       </c>
       <c r="L147">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.25">
@@ -11309,7 +11309,7 @@
         <v>17</v>
       </c>
       <c r="L148">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
@@ -11347,7 +11347,7 @@
         <v>17</v>
       </c>
       <c r="L149">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
@@ -11385,7 +11385,7 @@
         <v>17</v>
       </c>
       <c r="L150">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
@@ -11423,7 +11423,7 @@
         <v>17</v>
       </c>
       <c r="L151">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.25">
@@ -11461,7 +11461,7 @@
         <v>17</v>
       </c>
       <c r="L152">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
@@ -11499,7 +11499,7 @@
         <v>17</v>
       </c>
       <c r="L153">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
@@ -11537,7 +11537,7 @@
         <v>17</v>
       </c>
       <c r="L154">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
@@ -11575,7 +11575,7 @@
         <v>17</v>
       </c>
       <c r="L155">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
@@ -11613,7 +11613,7 @@
         <v>17</v>
       </c>
       <c r="L156">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
@@ -11651,7 +11651,7 @@
         <v>17</v>
       </c>
       <c r="L157">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
@@ -11689,7 +11689,7 @@
         <v>17</v>
       </c>
       <c r="L158">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
@@ -11727,7 +11727,7 @@
         <v>17</v>
       </c>
       <c r="L159">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
@@ -11765,7 +11765,7 @@
         <v>17</v>
       </c>
       <c r="L160">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
@@ -11803,7 +11803,7 @@
         <v>17</v>
       </c>
       <c r="L161">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
@@ -11841,7 +11841,7 @@
         <v>17</v>
       </c>
       <c r="L162">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
@@ -11879,7 +11879,7 @@
         <v>17</v>
       </c>
       <c r="L163">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
@@ -11917,7 +11917,7 @@
         <v>17</v>
       </c>
       <c r="L164">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
@@ -11955,7 +11955,7 @@
         <v>17</v>
       </c>
       <c r="L165">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
@@ -11993,7 +11993,7 @@
         <v>17</v>
       </c>
       <c r="L166">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
@@ -12031,7 +12031,7 @@
         <v>17</v>
       </c>
       <c r="L167">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
@@ -12069,7 +12069,7 @@
         <v>17</v>
       </c>
       <c r="L168">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.25">
@@ -12107,7 +12107,7 @@
         <v>17</v>
       </c>
       <c r="L169">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.25">
@@ -12145,7 +12145,7 @@
         <v>17</v>
       </c>
       <c r="L170">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.25">
@@ -12183,7 +12183,7 @@
         <v>17</v>
       </c>
       <c r="L171">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.25">
@@ -12221,7 +12221,7 @@
         <v>17</v>
       </c>
       <c r="L172">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.25">
@@ -12259,7 +12259,7 @@
         <v>17</v>
       </c>
       <c r="L173">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.25">
@@ -12297,7 +12297,7 @@
         <v>17</v>
       </c>
       <c r="L174">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.25">
@@ -12335,7 +12335,7 @@
         <v>17</v>
       </c>
       <c r="L175">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
